--- a/data/trans_dic/P57GLOBAL_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P57GLOBAL_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (tasa de respuesta: 98,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>56,34; 65,26</t>
+          <t>56,63; 65,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55,68; 65,11</t>
+          <t>55,96; 65,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73,64; 81,61</t>
+          <t>73,15; 81,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,48; 54,9</t>
+          <t>37,36; 54,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>58,65; 67,26</t>
+          <t>58,54; 67,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,51; 70,31</t>
+          <t>61,09; 70,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,41; 83,23</t>
+          <t>75,26; 83,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>41,63; 56,99</t>
+          <t>40,66; 56,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>58,82; 65,06</t>
+          <t>58,89; 65,09</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59,99; 66,63</t>
+          <t>60,14; 66,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75,36; 81,58</t>
+          <t>75,65; 81,37</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41,01; 53,13</t>
+          <t>41,65; 53,53</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,22; 71,45</t>
+          <t>64,28; 71,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,55; 68,79</t>
+          <t>61,67; 68,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77,95; 84,56</t>
+          <t>78,21; 84,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55,73; 68,57</t>
+          <t>56,1; 68,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>65,73; 72,93</t>
+          <t>65,95; 73,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,85; 76,39</t>
+          <t>69,07; 76,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,87; 84,15</t>
+          <t>77,85; 84,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,55; 56,93</t>
+          <t>29,31; 56,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>66,19; 71,17</t>
+          <t>65,98; 71,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66,26; 71,6</t>
+          <t>66,23; 71,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79,01; 83,58</t>
+          <t>78,93; 83,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>40,53; 60,07</t>
+          <t>42,68; 60,03</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66,74; 73,76</t>
+          <t>66,7; 73,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>67,82; 75,14</t>
+          <t>68,38; 75,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79,04; 84,98</t>
+          <t>79,12; 85,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58,88; 67,76</t>
+          <t>58,59; 67,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>67,44; 74,26</t>
+          <t>67,3; 74,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72,35; 79,0</t>
+          <t>72,05; 78,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79,55; 85,53</t>
+          <t>79,38; 85,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>57,03; 64,42</t>
+          <t>57,33; 64,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>68,26; 73,26</t>
+          <t>68,31; 73,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>71,36; 76,08</t>
+          <t>71,15; 76,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>80,16; 84,42</t>
+          <t>80,24; 84,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>59,38; 64,82</t>
+          <t>59,04; 64,6</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>68,62; 76,74</t>
+          <t>68,45; 76,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>66,58; 74,34</t>
+          <t>66,69; 74,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,73; 85,26</t>
+          <t>79,04; 85,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,59; 64,25</t>
+          <t>18,91; 64,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,05; 75,29</t>
+          <t>67,26; 75,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,87; 83,53</t>
+          <t>76,96; 83,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,5; 88,21</t>
+          <t>82,63; 88,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>53,78; 66,95</t>
+          <t>50,66; 66,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>69,28; 74,74</t>
+          <t>69,14; 74,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72,6; 78,19</t>
+          <t>72,76; 77,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81,66; 85,94</t>
+          <t>81,88; 86,17</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,02; 64,19</t>
+          <t>33,24; 63,78</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>67,94; 76,65</t>
+          <t>67,38; 76,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62,26; 71,97</t>
+          <t>62,0; 71,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79,85; 86,99</t>
+          <t>79,48; 86,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64,57; 72,17</t>
+          <t>64,73; 71,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>73,17; 81,21</t>
+          <t>73,27; 81,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,17; 78,82</t>
+          <t>70,82; 79,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,17; 89,85</t>
+          <t>83,18; 89,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>69,9; 75,67</t>
+          <t>69,68; 75,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>71,91; 77,98</t>
+          <t>71,47; 77,98</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68,22; 74,52</t>
+          <t>68,13; 74,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82,67; 87,5</t>
+          <t>82,63; 87,58</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>68,14; 72,81</t>
+          <t>68,25; 72,96</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>73,05; 82,28</t>
+          <t>73,05; 82,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69,2; 79,37</t>
+          <t>69,0; 79,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75,96; 84,83</t>
+          <t>75,75; 84,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>62,52; 71,04</t>
+          <t>63,17; 71,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>74,53; 82,6</t>
+          <t>73,79; 82,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72,62; 81,37</t>
+          <t>72,7; 81,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>86,9; 93,03</t>
+          <t>86,65; 92,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>63,93; 70,79</t>
+          <t>63,84; 70,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>74,94; 81,27</t>
+          <t>75,03; 81,48</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>72,47; 79,35</t>
+          <t>72,78; 79,3</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>82,61; 88,15</t>
+          <t>82,9; 88,1</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>64,45; 69,68</t>
+          <t>64,63; 69,74</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>75,46; 85,86</t>
+          <t>75,47; 86,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>71,68; 82,77</t>
+          <t>71,15; 82,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81,37; 89,3</t>
+          <t>81,23; 89,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67,64; 76,46</t>
+          <t>67,62; 76,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>77,03; 85,8</t>
+          <t>76,96; 85,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,02; 83,48</t>
+          <t>74,76; 83,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,48; 93,13</t>
+          <t>86,39; 92,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>72,54; 78,48</t>
+          <t>72,56; 78,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>78,0; 85,08</t>
+          <t>77,95; 84,91</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74,82; 81,94</t>
+          <t>75,18; 81,76</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>85,46; 90,76</t>
+          <t>85,62; 90,93</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>71,79; 76,71</t>
+          <t>71,61; 76,61</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>68,81; 71,98</t>
+          <t>68,8; 72,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>67,33; 70,42</t>
+          <t>67,28; 70,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>80,69; 83,38</t>
+          <t>80,46; 83,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44,53; 63,76</t>
+          <t>43,82; 63,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>70,65; 73,61</t>
+          <t>70,66; 73,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>73,71; 76,73</t>
+          <t>73,78; 76,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>83,36; 85,93</t>
+          <t>83,5; 86,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>58,44; 64,94</t>
+          <t>57,68; 64,72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>70,14; 72,39</t>
+          <t>70,2; 72,44</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>70,94; 73,25</t>
+          <t>71,07; 73,29</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82,45; 84,33</t>
+          <t>82,49; 84,22</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>51,76; 63,52</t>
+          <t>51,86; 63,55</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (tasa de respuesta: 98,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>277873; 321885</t>
+          <t>279316; 323103</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>249567; 291870</t>
+          <t>250840; 294142</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>308884; 342324</t>
+          <t>306856; 342816</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>148318; 217263</t>
+          <t>147864; 216368</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>274172; 314419</t>
+          <t>273667; 315562</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>262831; 300424</t>
+          <t>261054; 299491</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>297712; 328593</t>
+          <t>297131; 329664</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>127012; 173903</t>
+          <t>124064; 173800</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>565063; 625030</t>
+          <t>565751; 625298</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>525206; 583404</t>
+          <t>526585; 580470</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>613584; 664266</t>
+          <t>615979; 662558</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>287406; 372348</t>
+          <t>291946; 375164</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>472355; 525543</t>
+          <t>472737; 524808</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>418444; 467667</t>
+          <t>419253; 469068</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452441; 490780</t>
+          <t>453930; 491254</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>234501; 288538</t>
+          <t>236061; 289401</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>409696; 454622</t>
+          <t>411091; 456299</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>418689; 464535</t>
+          <t>420016; 464391</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>435498; 470589</t>
+          <t>435346; 470588</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>160442; 289519</t>
+          <t>149055; 288627</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>899465; 967031</t>
+          <t>896579; 966954</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>853390; 922239</t>
+          <t>853010; 920845</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>900456; 952478</t>
+          <t>899571; 950270</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>376657; 558254</t>
+          <t>396596; 557856</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>425541; 470287</t>
+          <t>425266; 470862</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>459054; 508604</t>
+          <t>462823; 508458</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>528161; 567841</t>
+          <t>528735; 568894</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>311335; 358278</t>
+          <t>309785; 354777</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>464503; 511466</t>
+          <t>463526; 512986</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>508991; 555731</t>
+          <t>506878; 555553</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>517237; 556137</t>
+          <t>516097; 553876</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>307654; 347534</t>
+          <t>309299; 347373</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>905313; 971707</t>
+          <t>905963; 969986</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>984979; 1050166</t>
+          <t>982118; 1050107</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1056803; 1112965</t>
+          <t>1057940; 1113072</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>634319; 692487</t>
+          <t>630743; 690121</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>355174; 397220</t>
+          <t>354309; 397825</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>405149; 452327</t>
+          <t>405810; 453265</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>503007; 544768</t>
+          <t>505013; 544781</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>180597; 563607</t>
+          <t>165931; 565903</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>345761; 388251</t>
+          <t>346838; 387186</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>469171; 509861</t>
+          <t>469707; 509495</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>530700; 567458</t>
+          <t>531577; 568832</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>376400; 468604</t>
+          <t>354545; 466871</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>715805; 772290</t>
+          <t>714336; 774286</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>884869; 953039</t>
+          <t>886878; 950362</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1047111; 1101911</t>
+          <t>1049940; 1104833</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>504994; 1012307</t>
+          <t>524314; 1005841</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>262167; 295773</t>
+          <t>259978; 296220</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>264091; 305301</t>
+          <t>262992; 303529</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>377294; 411032</t>
+          <t>375555; 410080</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>357896; 400027</t>
+          <t>358774; 398692</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>295589; 328078</t>
+          <t>295981; 329775</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>312051; 350526</t>
+          <t>314973; 351762</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>407535; 440256</t>
+          <t>407605; 440091</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>373583; 404424</t>
+          <t>372410; 404235</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>567990; 615941</t>
+          <t>564501; 615888</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>592802; 647514</t>
+          <t>591946; 646063</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>795763; 842254</t>
+          <t>795313; 842998</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>741866; 792641</t>
+          <t>743027; 794285</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>212445; 239303</t>
+          <t>212443; 240991</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>209732; 240556</t>
+          <t>209140; 240432</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>252428; 281905</t>
+          <t>251734; 281893</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>227221; 258188</t>
+          <t>229592; 259505</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>255587; 283251</t>
+          <t>253065; 282512</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>252369; 282777</t>
+          <t>252620; 283803</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>324732; 347643</t>
+          <t>323821; 347476</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>249482; 276259</t>
+          <t>249135; 274939</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>474943; 515070</t>
+          <t>475490; 516414</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>471507; 516249</t>
+          <t>473533; 515894</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>583259; 622391</t>
+          <t>585316; 621988</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>485761; 525130</t>
+          <t>487102; 525633</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>158372; 180205</t>
+          <t>158393; 180891</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>176051; 203304</t>
+          <t>174755; 203206</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>208404; 228721</t>
+          <t>208064; 228741</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>183144; 207003</t>
+          <t>183074; 206445</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>257219; 286488</t>
+          <t>256981; 286644</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>286144; 318417</t>
+          <t>285171; 317736</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>343775; 370197</t>
+          <t>343436; 369605</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>299079; 323557</t>
+          <t>299137; 323513</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424163; 462680</t>
+          <t>423895; 461741</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>469137; 513831</t>
+          <t>471438; 512714</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>558629; 593236</t>
+          <t>559651; 594387</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>490324; 523944</t>
+          <t>489099; 523289</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2250542; 2354164</t>
+          <t>2250039; 2355032</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2280017; 2384626</t>
+          <t>2278392; 2391339</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2717762; 2808146</t>
+          <t>2709949; 2805215</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1518941; 2174881</t>
+          <t>1494593; 2170174</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2385333; 2485211</t>
+          <t>2385562; 2491086</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2596683; 2703225</t>
+          <t>2599356; 2702639</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2924839; 3015188</t>
+          <t>2929722; 3018733</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1980925; 2201273</t>
+          <t>1955444; 2194019</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4661791; 4811229</t>
+          <t>4665905; 4815066</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4901721; 5060829</t>
+          <t>4910688; 5064090</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5669921; 5799050</t>
+          <t>5672689; 5791798</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3520377; 4320061</t>
+          <t>3527222; 4322024</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57GLOBAL_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P57GLOBAL_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>49,61%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>56,63; 65,51</t>
+          <t>56,9; 65,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55,96; 65,62</t>
+          <t>55,98; 65,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73,15; 81,73</t>
+          <t>74,0; 81,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,36; 54,67</t>
+          <t>39,01; 55,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>58,54; 67,5</t>
+          <t>58,54; 67,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,09; 70,09</t>
+          <t>60,65; 69,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,26; 83,5</t>
+          <t>75,68; 83,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40,66; 56,96</t>
+          <t>44,33; 59,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>58,89; 65,09</t>
+          <t>59,11; 65,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60,14; 66,3</t>
+          <t>60,16; 66,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75,65; 81,37</t>
+          <t>75,59; 81,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41,65; 53,53</t>
+          <t>43,96; 54,88</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>60,44%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,28; 71,36</t>
+          <t>64,21; 71,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,67; 68,99</t>
+          <t>61,07; 68,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78,21; 84,64</t>
+          <t>78,07; 84,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56,1; 68,77</t>
+          <t>58,17; 69,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>65,95; 73,2</t>
+          <t>65,38; 73,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,07; 76,37</t>
+          <t>68,98; 76,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,85; 84,15</t>
+          <t>77,24; 83,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,31; 56,76</t>
+          <t>51,85; 61,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65,98; 71,16</t>
+          <t>65,87; 71,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66,23; 71,5</t>
+          <t>66,24; 71,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78,93; 83,38</t>
+          <t>78,95; 83,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>42,68; 60,03</t>
+          <t>56,63; 64,35</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>63,86%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66,7; 73,85</t>
+          <t>66,16; 73,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68,38; 75,12</t>
+          <t>67,84; 75,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79,12; 85,13</t>
+          <t>79,13; 85,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58,59; 67,09</t>
+          <t>61,07; 69,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>67,3; 74,48</t>
+          <t>67,57; 74,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72,05; 78,97</t>
+          <t>72,07; 78,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79,38; 85,19</t>
+          <t>79,29; 85,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>57,33; 64,39</t>
+          <t>59,1; 65,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>68,31; 73,13</t>
+          <t>68,22; 73,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>71,15; 76,08</t>
+          <t>71,09; 76,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>80,24; 84,42</t>
+          <t>80,32; 84,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>59,04; 64,6</t>
+          <t>61,13; 66,52</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>64,95%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>68,45; 76,86</t>
+          <t>68,76; 76,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>66,69; 74,49</t>
+          <t>66,52; 74,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,04; 85,27</t>
+          <t>79,13; 85,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,91; 64,51</t>
+          <t>59,86; 67,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,26; 75,09</t>
+          <t>67,28; 75,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,96; 83,47</t>
+          <t>76,6; 83,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,63; 88,42</t>
+          <t>82,59; 87,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50,66; 66,71</t>
+          <t>62,84; 68,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>69,14; 74,94</t>
+          <t>69,22; 75,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72,76; 77,97</t>
+          <t>72,71; 77,84</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81,88; 86,17</t>
+          <t>81,7; 86,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>33,24; 63,78</t>
+          <t>62,78; 67,26</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>71,07%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>67,38; 76,77</t>
+          <t>67,64; 76,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62,0; 71,56</t>
+          <t>62,24; 71,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79,48; 86,79</t>
+          <t>79,88; 87,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64,73; 71,93</t>
+          <t>65,44; 72,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>73,27; 81,63</t>
+          <t>72,84; 81,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,82; 79,1</t>
+          <t>70,55; 79,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,18; 89,81</t>
+          <t>83,03; 89,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>69,68; 75,64</t>
+          <t>70,08; 76,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>71,47; 77,98</t>
+          <t>71,8; 78,01</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68,13; 74,35</t>
+          <t>67,72; 74,26</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82,63; 87,58</t>
+          <t>82,6; 87,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>68,25; 72,96</t>
+          <t>68,9; 73,4</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,56%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>73,05; 82,86</t>
+          <t>72,74; 82,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69,0; 79,33</t>
+          <t>69,32; 79,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75,75; 84,82</t>
+          <t>75,77; 84,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>63,17; 71,4</t>
+          <t>63,56; 71,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>73,79; 82,38</t>
+          <t>74,07; 82,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72,7; 81,67</t>
+          <t>73,36; 82,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>86,65; 92,98</t>
+          <t>86,54; 93,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>63,84; 70,46</t>
+          <t>64,68; 70,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75,03; 81,48</t>
+          <t>74,88; 81,19</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>72,78; 79,3</t>
+          <t>72,68; 79,45</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>82,9; 88,1</t>
+          <t>82,84; 88,12</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>64,63; 69,74</t>
+          <t>65,01; 70,21</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,35%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>75,47; 86,19</t>
+          <t>75,4; 85,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>71,15; 82,73</t>
+          <t>71,96; 82,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81,23; 89,31</t>
+          <t>81,52; 89,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67,62; 76,25</t>
+          <t>67,98; 76,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,96; 85,85</t>
+          <t>77,64; 86,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,76; 83,3</t>
+          <t>74,73; 83,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,39; 92,98</t>
+          <t>86,22; 93,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>72,56; 78,47</t>
+          <t>72,42; 78,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>77,95; 84,91</t>
+          <t>78,56; 84,95</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75,18; 81,76</t>
+          <t>74,82; 81,86</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>85,62; 90,93</t>
+          <t>85,14; 90,6</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>71,61; 76,61</t>
+          <t>71,93; 76,82</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>64,84%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>68,8; 72,01</t>
+          <t>68,69; 71,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>67,28; 70,62</t>
+          <t>67,23; 70,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>80,46; 83,29</t>
+          <t>80,47; 83,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43,82; 63,62</t>
+          <t>62,57; 66,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>70,66; 73,79</t>
+          <t>70,83; 73,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>73,78; 76,72</t>
+          <t>73,9; 76,69</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>83,5; 86,03</t>
+          <t>83,39; 85,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>57,68; 64,72</t>
+          <t>63,9; 66,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>70,2; 72,44</t>
+          <t>70,27; 72,46</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>71,07; 73,29</t>
+          <t>71,04; 73,28</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82,49; 84,22</t>
+          <t>82,36; 84,23</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>51,86; 63,55</t>
+          <t>63,67; 66,08</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>181907</t>
+          <t>192829</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>149340</t>
+          <t>183204</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>331246</t>
+          <t>376033</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>279316; 323103</t>
+          <t>280634; 324388</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>250840; 294142</t>
+          <t>250946; 294390</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>306856; 342816</t>
+          <t>310408; 343800</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>147864; 216368</t>
+          <t>157330; 224661</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>273667; 315562</t>
+          <t>273667; 314662</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>261054; 299491</t>
+          <t>259175; 298164</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>297131; 329664</t>
+          <t>298774; 328887</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>124064; 173800</t>
+          <t>157206; 209369</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>565751; 625298</t>
+          <t>567861; 627446</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>526585; 580470</t>
+          <t>526689; 584316</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>615979; 662558</t>
+          <t>615464; 661798</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>291946; 375164</t>
+          <t>333137; 415919</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>263560</t>
+          <t>304905</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>241730</t>
+          <t>281623</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>505290</t>
+          <t>586529</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>472737; 524808</t>
+          <t>472277; 524702</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>419253; 469068</t>
+          <t>415227; 466816</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>453930; 491254</t>
+          <t>453123; 490085</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>236061; 289401</t>
+          <t>275774; 330749</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>411091; 456299</t>
+          <t>407515; 455177</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>420016; 464391</t>
+          <t>419475; 463645</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>435346; 470588</t>
+          <t>431946; 468852</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>149055; 288627</t>
+          <t>257332; 305127</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>896579; 966954</t>
+          <t>895088; 966699</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>853010; 920845</t>
+          <t>853201; 920170</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>899571; 950270</t>
+          <t>899728; 951981</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>396596; 557856</t>
+          <t>549596; 624456</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>333319</t>
+          <t>397931</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>328152</t>
+          <t>387038</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>661471</t>
+          <t>784968</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>425266; 470862</t>
+          <t>421793; 469930</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>462823; 508458</t>
+          <t>459193; 509112</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>528735; 568894</t>
+          <t>528772; 569379</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>309785; 354777</t>
+          <t>372906; 424259</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>463526; 512986</t>
+          <t>465425; 513767</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>506878; 555553</t>
+          <t>506997; 554777</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>516097; 553876</t>
+          <t>515508; 553577</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>309299; 347373</t>
+          <t>365530; 407696</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>905963; 969986</t>
+          <t>904819; 971835</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>982118; 1050107</t>
+          <t>981222; 1049072</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1057940; 1113072</t>
+          <t>1058989; 1113324</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>630743; 690121</t>
+          <t>751381; 817582</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>398969</t>
+          <t>439642</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>437911</t>
+          <t>477288</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>836880</t>
+          <t>916930</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>354309; 397825</t>
+          <t>355903; 397644</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>405810; 453265</t>
+          <t>404781; 453215</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>505013; 544781</t>
+          <t>505606; 545486</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>165931; 565903</t>
+          <t>412323; 463690</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>346838; 387186</t>
+          <t>346908; 389480</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>469707; 509495</t>
+          <t>467517; 508944</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>531577; 568832</t>
+          <t>531321; 565077</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>354545; 466871</t>
+          <t>454231; 496354</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>714336; 774286</t>
+          <t>715165; 776396</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>886878; 950362</t>
+          <t>886171; 948716</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1049940; 1104833</t>
+          <t>1047528; 1103563</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>524314; 1005841</t>
+          <t>886202; 949443</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>378909</t>
+          <t>415993</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>388673</t>
+          <t>433940</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>767581</t>
+          <t>849933</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>259978; 296220</t>
+          <t>261008; 296583</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>262992; 303529</t>
+          <t>264030; 304339</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>375555; 410080</t>
+          <t>377462; 411518</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>358774; 398692</t>
+          <t>394249; 438592</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>295981; 329775</t>
+          <t>294282; 328266</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>314973; 351762</t>
+          <t>313752; 352162</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>407605; 440091</t>
+          <t>406850; 439018</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>372410; 404235</t>
+          <t>415861; 451171</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>564501; 615888</t>
+          <t>567079; 616141</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>591946; 646063</t>
+          <t>588462; 645223</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>795313; 842998</t>
+          <t>795056; 842662</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>743027; 794285</t>
+          <t>823956; 877825</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>244351</t>
+          <t>270949</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>262731</t>
+          <t>289125</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>507082</t>
+          <t>560074</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>212443; 240991</t>
+          <t>211548; 239303</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>209140; 240432</t>
+          <t>210119; 240946</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>251734; 281893</t>
+          <t>251813; 281908</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>229592; 259505</t>
+          <t>255727; 286585</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>253065; 282512</t>
+          <t>254025; 283181</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>252620; 283803</t>
+          <t>254924; 284933</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>323821; 347476</t>
+          <t>323419; 347532</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>249135; 274939</t>
+          <t>275958; 301741</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>475490; 516414</t>
+          <t>474566; 514557</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>473533; 515894</t>
+          <t>472823; 516920</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>585316; 621988</t>
+          <t>584849; 622161</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>487102; 525633</t>
+          <t>538947; 582036</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>195457</t>
+          <t>215956</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>311528</t>
+          <t>340115</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>506985</t>
+          <t>556071</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>158393; 180891</t>
+          <t>158260; 180133</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>174755; 203206</t>
+          <t>176738; 203309</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>208064; 228741</t>
+          <t>208801; 228264</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>183074; 206445</t>
+          <t>202329; 227913</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>256981; 286644</t>
+          <t>259249; 287911</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>285171; 317736</t>
+          <t>285032; 317118</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>343436; 369605</t>
+          <t>342733; 370237</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>299137; 323513</t>
+          <t>326105; 353332</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>423895; 461741</t>
+          <t>427209; 461943</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>471438; 512714</t>
+          <t>469151; 513285</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>559651; 594387</t>
+          <t>556536; 592241</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>489099; 523289</t>
+          <t>537999; 574524</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1996471</t>
+          <t>2238205</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2120065</t>
+          <t>2392335</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4116536</t>
+          <t>4630539</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2250039; 2355032</t>
+          <t>2246459; 2354550</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2278392; 2391339</t>
+          <t>2276496; 2387681</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2709949; 2805215</t>
+          <t>2710225; 2804228</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1494593; 2170174</t>
+          <t>2176876; 2301574</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2385562; 2491086</t>
+          <t>2391150; 2493440</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2599356; 2702639</t>
+          <t>2603273; 2701715</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2929722; 3018733</t>
+          <t>2925991; 3014856</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1955444; 2194019</t>
+          <t>2340477; 2443956</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4665905; 4815066</t>
+          <t>4670773; 4816316</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4910688; 5064090</t>
+          <t>4908312; 5063081</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5672689; 5791798</t>
+          <t>5663488; 5792360</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3527222; 4322024</t>
+          <t>4547219; 4719049</t>
         </is>
       </c>
     </row>
